--- a/Notes/17_kNN_NormsDemo.xlsx
+++ b/Notes/17_kNN_NormsDemo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\michael.olson2\Documents\GitHubs\math3080\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B92DDA7-077A-4295-8D54-DD6F789203C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1742B95-2324-438A-8ADF-510D0BF6B9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{EDC99FF8-BC4A-4F25-82BC-631685136885}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15943" xr2:uid="{EDC99FF8-BC4A-4F25-82BC-631685136885}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -459,7 +459,7 @@
       </c>
       <c r="F1" t="str">
         <f t="shared" ref="F1:U1" si="0">IF(F2="","",_xlfn.CONCAT("L",F2,"-norm"))</f>
-        <v/>
+        <v>L3-norm</v>
       </c>
       <c r="G1" t="str">
         <f t="shared" si="0"/>
@@ -535,7 +535,9 @@
       <c r="E2" s="1">
         <v>2</v>
       </c>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1">
+        <v>3</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -567,9 +569,9 @@
         <f>IF(E2="","",ABS($B3-$A3)^E$2)</f>
         <v>1.0000000000000018E-2</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F3">
         <f t="shared" ref="F3:F22" si="1">IF(F2="","",ABS($B3-$A3)^F$2)</f>
-        <v/>
+        <v>1.0000000000000026E-3</v>
       </c>
       <c r="G3" t="str">
         <f t="shared" ref="G3:G22" si="2">IF(G2="","",ABS($B3-$A3)^G$2)</f>
@@ -640,16 +642,16 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:I22" si="15">ABS($B4-$A4)^D$2</f>
+        <f t="shared" ref="D4:D22" si="15">ABS($B4-$A4)^D$2</f>
         <v>0.20000000000000018</v>
       </c>
       <c r="E4">
         <f t="shared" ref="E4:E22" si="16">IF(E3="","",ABS($B4-$A4)^E$2)</f>
         <v>4.000000000000007E-2</v>
       </c>
-      <c r="F4" t="str">
+      <c r="F4">
         <f t="shared" si="1"/>
-        <v/>
+        <v>8.000000000000021E-3</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" si="2"/>
@@ -727,9 +729,9 @@
         <f t="shared" si="16"/>
         <v>8.99999999999999E-2</v>
       </c>
-      <c r="F5" t="str">
+      <c r="F5">
         <f t="shared" si="1"/>
-        <v/>
+        <v>2.6999999999999955E-2</v>
       </c>
       <c r="G5" t="str">
         <f t="shared" si="2"/>
@@ -807,9 +809,9 @@
         <f t="shared" si="16"/>
         <v>0.16000000000000028</v>
       </c>
-      <c r="F6" t="str">
+      <c r="F6">
         <f t="shared" si="1"/>
-        <v/>
+        <v>6.4000000000000168E-2</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" si="2"/>
@@ -887,9 +889,9 @@
         <f t="shared" si="16"/>
         <v>0.25</v>
       </c>
-      <c r="F7" t="str">
+      <c r="F7">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.125</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="2"/>
@@ -967,9 +969,9 @@
         <f t="shared" si="16"/>
         <v>0.3599999999999996</v>
       </c>
-      <c r="F8" t="str">
+      <c r="F8">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.21599999999999964</v>
       </c>
       <c r="G8" t="str">
         <f t="shared" si="2"/>
@@ -1047,9 +1049,9 @@
         <f t="shared" si="16"/>
         <v>0.49000000000000027</v>
       </c>
-      <c r="F9" t="str">
+      <c r="F9">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.34300000000000025</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" si="2"/>
@@ -1127,9 +1129,9 @@
         <f t="shared" si="16"/>
         <v>0.64000000000000112</v>
       </c>
-      <c r="F10" t="str">
+      <c r="F10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.51200000000000134</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" si="2"/>
@@ -1207,9 +1209,9 @@
         <f t="shared" si="16"/>
         <v>0.81000000000000061</v>
       </c>
-      <c r="F11" t="str">
+      <c r="F11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.72900000000000087</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" si="2"/>
@@ -1287,9 +1289,9 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="F12" t="str">
+      <c r="F12">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" si="2"/>
@@ -1367,9 +1369,9 @@
         <f t="shared" si="16"/>
         <v>1.2099999999999993</v>
       </c>
-      <c r="F13" t="str">
+      <c r="F13">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1.3309999999999989</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="2"/>
@@ -1447,9 +1449,9 @@
         <f t="shared" si="16"/>
         <v>1.4399999999999984</v>
       </c>
-      <c r="F14" t="str">
+      <c r="F14">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1.7279999999999971</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" si="2"/>
@@ -1527,9 +1529,9 @@
         <f t="shared" si="16"/>
         <v>1.6900000000000019</v>
       </c>
-      <c r="F15" t="str">
+      <c r="F15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>2.1970000000000036</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" si="2"/>
@@ -1607,9 +1609,9 @@
         <f t="shared" si="16"/>
         <v>1.9600000000000011</v>
       </c>
-      <c r="F16" t="str">
+      <c r="F16">
         <f t="shared" si="1"/>
-        <v/>
+        <v>2.744000000000002</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" si="2"/>
@@ -1687,9 +1689,9 @@
         <f t="shared" si="16"/>
         <v>2.25</v>
       </c>
-      <c r="F17" t="str">
+      <c r="F17">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3.375</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" si="2"/>
@@ -1767,9 +1769,9 @@
         <f t="shared" si="16"/>
         <v>2.5600000000000045</v>
       </c>
-      <c r="F18" t="str">
+      <c r="F18">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4.0960000000000107</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" si="2"/>
@@ -1847,9 +1849,9 @@
         <f t="shared" si="16"/>
         <v>2.8899999999999975</v>
       </c>
-      <c r="F19" t="str">
+      <c r="F19">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4.912999999999994</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
@@ -1927,9 +1929,9 @@
         <f t="shared" si="16"/>
         <v>3.2400000000000024</v>
       </c>
-      <c r="F20" t="str">
+      <c r="F20">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5.832000000000007</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" si="2"/>
@@ -2007,9 +2009,9 @@
         <f t="shared" si="16"/>
         <v>3.6099999999999945</v>
       </c>
-      <c r="F21" t="str">
+      <c r="F21">
         <f t="shared" si="1"/>
-        <v/>
+        <v>6.8589999999999849</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" si="2"/>
@@ -2087,9 +2089,9 @@
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
-      <c r="F22" t="str">
+      <c r="F22">
         <f t="shared" si="1"/>
-        <v/>
+        <v>8</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" si="2"/>
@@ -2164,9 +2166,9 @@
         <f>IF(E2="","",SUM(E3:E22))</f>
         <v>28.700000000000003</v>
       </c>
-      <c r="F25" t="str">
+      <c r="F25">
         <f t="shared" ref="F25:U25" si="17">IF(F2="","",SUM(F3:F22))</f>
-        <v/>
+        <v>44.1</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="17"/>
@@ -2241,9 +2243,9 @@
         <f>IF(E2="","",E25^(1/E2))</f>
         <v>5.3572380943915494</v>
       </c>
-      <c r="F27" t="str">
+      <c r="F27">
         <f t="shared" ref="F27:U27" si="18">IF(F2="","",F25^(1/F2))</f>
-        <v/>
+        <v>3.5330208180539455</v>
       </c>
       <c r="G27" t="str">
         <f t="shared" si="18"/>
